--- a/data/measures-of-central-tendency--salaries.xlsx
+++ b/data/measures-of-central-tendency--salaries.xlsx
@@ -5652,14 +5652,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>annual_salary is right-skewed: a handful of senior/executive salaries pull the mean above the median, the chapter's core lesson.</t>
+          <t>annual_salary is right-skewed: a handful of senior and lead salaries pull the mean above the median, the chapter's core lesson.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>department and job_level are categorical, so their typical value is a mode, not a mean.</t>
+          <t>department is an unordered category, so its typical value is a mode. job_level is ordered, so it has a median as well.</t>
         </is>
       </c>
     </row>
